--- a/output/pdf_financials_xlsx/SME.xlsx
+++ b/output/pdf_financials_xlsx/SME.xlsx
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.528349</v>
+        <v>-2.528349</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.905792</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.528349</v>
+        <v>-2.528349</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.905792</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.528349</v>
+        <v>-2.528349</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.905792</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-84.2783</v>
+        <v>84.2783</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.528349</v>
+        <v>-2.528349</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.905792</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.537448</v>
+        <v>-2.51925</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.900484</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8341.106472502548</v>
+        <v>-8281.285953781926</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-1027.527500114109</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-101.3911582350032</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>8311.196213142237</v>
+        <v>-8311.196213142237</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-1033.584371719385</v>
@@ -7162,22 +7162,22 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.792911</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-1.091551</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.836534</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>-0.039578</v>
+        <v>-3.21316</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>-0.025</v>
+        <v>-2.923743</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-4.760799</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -19898,7 +19898,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -40314,7 +40318,11 @@
           <t>Exploration and evaluation expenditures 11</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -41842,7 +41850,11 @@
           <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -43468,7 +43480,11 @@
           <t>Exploration and evaluation expenditures 9 and 13</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -45374,7 +45390,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -76810,10 +76830,10 @@
         </is>
       </c>
       <c r="K724" s="5" t="n">
-        <v>2.528349</v>
+        <v>-2.528349</v>
       </c>
       <c r="L724" s="5" t="n">
-        <v>0.905792</v>
+        <v>-0.905792</v>
       </c>
       <c r="M724" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SME.xlsx
+++ b/output/pdf_financials_xlsx/SME.xlsx
@@ -1028,55 +1028,53 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.02202</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.03639</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.036802</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.026715</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000123</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.009119</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00016</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000128</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.007593</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.077817</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.123916</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.073363</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.122665</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.171799</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.093094</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.027752</v>
       </c>
     </row>
     <row r="13">
@@ -2047,10 +2045,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.326168</v>
+        <v>-0.362558</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.234829</v>
+        <v>-0.271631</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2068,34 +2066,34 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.528349</v>
+        <v>-2.528189</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.905792</v>
+        <v>-0.9059199999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>24.707251</v>
+        <v>24.699658</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.349681</v>
+        <v>-3.427498</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-13.718516</v>
+        <v>-13.842432</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.307404</v>
+        <v>-3.380767</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.608867</v>
+        <v>0.486202</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.144016</v>
+        <v>-5.315815</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>11.9536</v>
+        <v>11.860506</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.430229</v>
+        <v>1.402477</v>
       </c>
     </row>
     <row r="28">
@@ -2165,10 +2163,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.326168</v>
+        <v>-0.362558</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.164427</v>
+        <v>-0.201229</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2186,34 +2184,34 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.51925</v>
+        <v>-2.51909</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.900484</v>
+        <v>-0.900612</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>24.714781</v>
+        <v>24.707188</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.32674</v>
+        <v>-3.404557</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-13.694431</v>
+        <v>-13.818347</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.957247</v>
+        <v>-3.03061</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.960069</v>
+        <v>0.837404</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.796935</v>
+        <v>-4.968734</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>12.033216</v>
+        <v>11.940122</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.438115</v>
+        <v>1.410363</v>
       </c>
     </row>
     <row r="30">
@@ -2228,10 +2226,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-232.0852723106918</v>
+        <v>-257.9786249982211</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-170.4524957238377</v>
+        <v>-208.6031203027005</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2249,19 +2247,19 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-8281.285953781926</v>
+        <v>-8280.760001314882</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-1027.527500114109</v>
+        <v>-1027.673558811447</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>131008.6456400742</v>
+        <v>130968.3965014577</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-746.4313440404231</v>
+        <v>-763.8913943897721</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-53921.45135252196</v>
+        <v>-54409.36724810017</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -7521,7 +7519,7 @@
         <v>0</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.04873</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7576,7 +7574,7 @@
         <v>0</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.04873</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -22172,7 +22170,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -31882,7 +31880,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -55324,7 +55326,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -76508,7 +76510,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -79114,7 +79116,7 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
@@ -80254,7 +80256,7 @@
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
@@ -81124,7 +81126,7 @@
       </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E769" t="inlineStr">
@@ -82182,7 +82184,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -83908,7 +83910,7 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
@@ -85052,7 +85054,7 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E810" s="5" t="n">

--- a/output/pdf_financials_xlsx/SME.xlsx
+++ b/output/pdf_financials_xlsx/SME.xlsx
@@ -6836,7 +6836,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.226948</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.01319</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -40224,7 +40224,11 @@
           <t>Proceeds from the disposal of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -43386,7 +43390,11 @@
           <t>Proceeds from disposal of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -45296,7 +45304,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SME.xlsx
+++ b/output/pdf_financials_xlsx/SME.xlsx
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.55689</v>
+        <v>0.58289</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.64523</v>
+        <v>0.65173</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.284766</v>
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.0596</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.044058</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.037744</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -40422,7 +40422,11 @@
           <t>Issuance of units under a private placement 12</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -40708,7 +40712,11 @@
           <t>Deferred tax expense 12</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -49038,7 +49046,11 @@
           <t>Cash proceeds from private placement</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -49134,7 +49146,11 @@
           <t>Share issue costs related to private placement (Note 8)</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -50176,7 +50192,11 @@
           <t>Cash proceeds from private placement (Note 8 and 9)</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -52568,7 +52588,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -52664,7 +52688,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -54194,7 +54222,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E486" s="5" t="n">
         <v>-0.0596</v>
       </c>
@@ -76040,7 +76072,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E716" t="inlineStr">
         <is>
           <t>-</t>
@@ -76072,7 +76108,7 @@
         </is>
       </c>
       <c r="K716" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0065</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
@@ -78358,7 +78394,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D740" t="inlineStr"/>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E740" t="inlineStr">
         <is>
           <t>-</t>
@@ -78388,7 +78428,7 @@
         <v>0.026</v>
       </c>
       <c r="K740" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0065</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>
